--- a/InputData/dist-heat/EoCtUH/na-Efficiency of Conversion to Usable Heat.xlsx
+++ b/InputData/dist-heat/EoCtUH/na-Efficiency of Conversion to Usable Heat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\工作文件\eps同步\eps4.0-china-smart-trans\InputData\dist-heat\EoCtUH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EPS in github\Github China\eps-china2019-smart-trans\InputData\dist-heat\EoCtUH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5F6A6D-4C6B-4A2E-8330-EF11772ED5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB474071-476A-41D4-99E2-C60E96496505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{4BAF35DA-4A3D-48F0-8B20-147DF0AACC53}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="27045" windowHeight="13485" activeTab="3" xr2:uid="{4BAF35DA-4A3D-48F0-8B20-147DF0AACC53}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>Source:</t>
   </si>
@@ -354,6 +354,30 @@
   </si>
   <si>
     <t>Obtain data directly from the literature</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020年全国能源平衡表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>供热净投入</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>万吨标煤</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>供热产出</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>转化效率</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>供热总投入</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -893,19 +917,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F64CA3-E883-4FBE-8F70-B562D6180682}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="46.44140625" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="46.5" customWidth="1"/>
+    <col min="8" max="8" width="30.75" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>92</v>
       </c>
@@ -913,12 +937,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>2018</v>
       </c>
@@ -926,7 +950,7 @@
       <c r="J5" s="13"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>96</v>
       </c>
@@ -934,7 +958,7 @@
       <c r="J6" s="13"/>
       <c r="M6" s="13"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>95</v>
       </c>
@@ -942,37 +966,37 @@
       <c r="J7" s="13"/>
       <c r="M7" s="13"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>98</v>
       </c>
       <c r="J9" s="13"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
         <v>2019</v>
       </c>
       <c r="J10" s="13"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>97</v>
       </c>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
         <v>95</v>
       </c>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -983,16 +1007,16 @@
       <c r="J14" s="16"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="I15" s="15"/>
       <c r="J15" s="16"/>
       <c r="K15" s="13"/>
       <c r="M15" s="13"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
     </row>
   </sheetData>
@@ -1005,19 +1029,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="47.44140625" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="47.5" customWidth="1"/>
+    <col min="8" max="8" width="30.75" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,12 +1058,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>2014</v>
       </c>
@@ -1056,7 +1080,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -1070,7 +1094,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B7" s="11" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1108,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>11</v>
       </c>
@@ -1101,7 +1125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="I9" t="s">
         <v>57</v>
       </c>
@@ -1109,7 +1133,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
@@ -1123,7 +1147,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -1134,7 +1158,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
         <v>2018</v>
       </c>
@@ -1145,7 +1169,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -1156,7 +1180,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
@@ -1170,7 +1194,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B15" s="12"/>
       <c r="I15" s="15" t="s">
         <v>89</v>
@@ -1183,7 +1207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1191,7 +1215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1199,7 +1223,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1207,7 +1231,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1215,7 +1239,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1223,7 +1247,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1231,7 +1255,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1239,7 +1263,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1247,7 +1271,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1255,12 +1279,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1271,7 +1295,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
       <c r="I29" t="s">
         <v>80</v>
       </c>
@@ -1285,7 +1309,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
@@ -1302,12 +1326,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1326,19 +1350,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="46.44140625" customWidth="1"/>
-    <col min="3" max="3" width="32.88671875" customWidth="1"/>
+    <col min="1" max="1" width="46.5" customWidth="1"/>
+    <col min="3" max="3" width="32.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -1360,8 +1384,11 @@
       <c r="G2" s="1">
         <v>2012</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>0.65</v>
       </c>
@@ -1383,26 +1410,63 @@
       <c r="G3">
         <v>0.73</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3">
+        <v>7202.87</v>
+      </c>
+      <c r="K3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4">
+        <v>20934.21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5">
+        <f>J3+J4</f>
+        <v>28137.079999999998</v>
+      </c>
+      <c r="K5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
         <f>AVERAGE(A3:G3)</f>
         <v>0.7014285714285714</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6">
+        <f>J4/J5</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1413,7 +1477,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1424,7 +1488,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1435,7 +1499,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1446,7 +1510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>4</v>
       </c>
@@ -1457,7 +1521,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>5</v>
       </c>
@@ -1468,7 +1532,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>6</v>
       </c>
@@ -1479,7 +1543,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1490,7 +1554,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1501,7 +1565,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>9</v>
       </c>
@@ -1512,7 +1576,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>10</v>
       </c>
@@ -1523,7 +1587,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>11</v>
       </c>
@@ -1534,7 +1598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>12</v>
       </c>
@@ -1545,7 +1609,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>13</v>
       </c>
@@ -1556,7 +1620,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>14</v>
       </c>
@@ -1567,7 +1631,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>15</v>
       </c>
@@ -1578,7 +1642,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>16</v>
       </c>
@@ -1589,7 +1653,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>50</v>
       </c>
@@ -1598,17 +1662,17 @@
         <v>3.6642857142857141</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
@@ -1629,18 +1693,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.625" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1649,85 +1713,85 @@
         <v>3.6642857142857141</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
+        <f>Data!$J$6</f>
+        <v>0.744007907003854</v>
       </c>
     </row>
   </sheetData>
